--- a/assingment/excel assingment/session - 12/SESSION -12.xlsx
+++ b/assingment/excel assingment/session - 12/SESSION -12.xlsx
@@ -1,27 +1,266 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\assingment\excel assingment\session - 12\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F2DCF7-E7C7-422F-BEE3-80E15D3CFB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK - 1" sheetId="1" r:id="rId1"/>
+    <sheet name="TASK - 2" sheetId="2" r:id="rId2"/>
+    <sheet name="TASK -3" sheetId="3" r:id="rId3"/>
+    <sheet name="TASK - 4" sheetId="4" r:id="rId4"/>
+    <sheet name="TASK - 5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+  <si>
+    <t>Song Name</t>
+  </si>
+  <si>
+    <t>Artist</t>
+  </si>
+  <si>
+    <t>Kesariya</t>
+  </si>
+  <si>
+    <t>Arijit Singh</t>
+  </si>
+  <si>
+    <t>Chaleya</t>
+  </si>
+  <si>
+    <t>Apna Bana Le</t>
+  </si>
+  <si>
+    <t>Tum Hi Ho</t>
+  </si>
+  <si>
+    <t>Pasoori</t>
+  </si>
+  <si>
+    <t>Ali Sethi</t>
+  </si>
+  <si>
+    <t>Heeriye</t>
+  </si>
+  <si>
+    <t>Raataan Lambiyan</t>
+  </si>
+  <si>
+    <t>Jubin Nautiyal</t>
+  </si>
+  <si>
+    <t>Tere Vaaste</t>
+  </si>
+  <si>
+    <t>Varun Jain</t>
+  </si>
+  <si>
+    <t>O Maahi</t>
+  </si>
+  <si>
+    <t>Ve Kamleya</t>
+  </si>
+  <si>
+    <t>Kalank</t>
+  </si>
+  <si>
+    <t>Shayad</t>
+  </si>
+  <si>
+    <t>Channa Mereya</t>
+  </si>
+  <si>
+    <t>Tum Se Hi</t>
+  </si>
+  <si>
+    <t>Mohit Chauhan</t>
+  </si>
+  <si>
+    <t>Satranga</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>iPhone 15</t>
+  </si>
+  <si>
+    <t>Galaxy S24</t>
+  </si>
+  <si>
+    <t>OnePlus 12</t>
+  </si>
+  <si>
+    <t>Pixel 9</t>
+  </si>
+  <si>
+    <t>Vivo X200</t>
+  </si>
+  <si>
+    <t>Realme GT</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Domino's</t>
+  </si>
+  <si>
+    <t>McDonald's</t>
+  </si>
+  <si>
+    <t>KFC</t>
+  </si>
+  <si>
+    <t>Pizza Hut</t>
+  </si>
+  <si>
+    <t>Burger King</t>
+  </si>
+  <si>
+    <t>La Pino'z</t>
+  </si>
+  <si>
+    <t>Subway</t>
+  </si>
+  <si>
+    <t>Wow Momo</t>
+  </si>
+  <si>
+    <t>Hocco</t>
+  </si>
+  <si>
+    <t>Bikanervala</t>
+  </si>
+  <si>
+    <t>Sizzling Joe</t>
+  </si>
+  <si>
+    <t>Honest</t>
+  </si>
+  <si>
+    <t>Havmor</t>
+  </si>
+  <si>
+    <t>Gopal Locho</t>
+  </si>
+  <si>
+    <t>Gwalia</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Runs</t>
+  </si>
+  <si>
+    <t>Virat Kohli</t>
+  </si>
+  <si>
+    <t>Shubman Gill</t>
+  </si>
+  <si>
+    <t>Ruturaj Gaikwad</t>
+  </si>
+  <si>
+    <t>Rohit Sharma</t>
+  </si>
+  <si>
+    <t>KL Rahul</t>
+  </si>
+  <si>
+    <t>Sanju Samson</t>
+  </si>
+  <si>
+    <t>Hardik Pandya</t>
+  </si>
+  <si>
+    <t>MS Dhoni</t>
+  </si>
+  <si>
+    <t>Rinku Singh</t>
+  </si>
+  <si>
+    <t>Rahul Tripathi</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Swiggy</t>
+  </si>
+  <si>
+    <t>Myntra</t>
+  </si>
+  <si>
+    <t>Paytm</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Netflix</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,13 +288,94 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -330,10 +650,660 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:B21">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4FCDDE-0BDE-4A70-A9AF-C9430B1AA4C7}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3">
+        <v>42000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE158CC8-F101-47D8-BFDB-DFEC6C5145E7}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C1:C16">
+    <cfRule type="iconSet" priority="2">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="1">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="4"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B65A8647-0DBC-486C-9E7E-131250EDF84D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="3">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B11">
+    <cfRule type="top10" dxfId="1" priority="3" rank="3"/>
+    <cfRule type="top10" dxfId="2" priority="2" rank="3"/>
+    <cfRule type="top10" dxfId="3" priority="1" bottom="1" rank="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD8F988-23CC-4E0D-90C9-12F004E79777}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3">
+        <v>700</v>
+      </c>
+      <c r="C6" s="3">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2500</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C7">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C2&lt;=$B2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>